--- a/data/trans_bre/P36B08_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>-0,22%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,07</t>
+          <t>-3,49; 9,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,51</t>
+          <t>5,21; 19,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,77</t>
+          <t>-5,72; 8,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 7,71</t>
+          <t>-5,69; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 19,08</t>
+          <t>-6,45; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,58; 41,15</t>
+          <t>10,02; 40,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 15,49</t>
+          <t>-8,75; 13,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 8,9</t>
+          <t>-6,01; 6,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,25</t>
+          <t>2,05; 12,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,45</t>
+          <t>3,05; 13,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,46</t>
+          <t>-1,55; 8,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,88</t>
+          <t>-1,91; 4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,72</t>
+          <t>3,19; 20,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 20,76</t>
+          <t>4,46; 20,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 14,31</t>
+          <t>-2,06; 13,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,33</t>
+          <t>-1,96; 5,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 15,99</t>
+          <t>5,92; 15,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,01</t>
+          <t>2,57; 12,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,6</t>
+          <t>2,08; 11,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,55</t>
+          <t>-0,39; 4,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 27,49</t>
+          <t>9,4; 26,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 16,85</t>
+          <t>3,69; 17,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,86</t>
+          <t>2,88; 17,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,94</t>
+          <t>-0,41; 4,77</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 18,08</t>
+          <t>7,26; 18,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,37</t>
+          <t>5,39; 15,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,95</t>
+          <t>4,24; 14,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,78</t>
+          <t>-0,53; 3,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 30,24</t>
+          <t>10,78; 30,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 22,11</t>
+          <t>7,26; 22,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,44</t>
+          <t>5,67; 21,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,95</t>
+          <t>-0,55; 3,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 10,2</t>
+          <t>-2,5; 10,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 11,1</t>
+          <t>-0,89; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 10,27</t>
+          <t>-0,44; 10,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,6</t>
+          <t>0,56; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 14,98</t>
+          <t>-3,49; 15,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 15,37</t>
+          <t>-1,18; 14,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 13,77</t>
+          <t>-0,68; 13,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,09</t>
+          <t>0,59; 5,68</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 12,09</t>
+          <t>-1,39; 11,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 11,16</t>
+          <t>-0,37; 11,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 10,34</t>
+          <t>-1,81; 9,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,7</t>
+          <t>-0,75; 3,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 17,71</t>
+          <t>-1,82; 17,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 14,38</t>
+          <t>-0,33; 14,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 13,49</t>
+          <t>-2,18; 12,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,1</t>
+          <t>-0,77; 4,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,48%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,38</t>
+          <t>-6,08; 8,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 7,65</t>
+          <t>-5,08; 7,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,38</t>
+          <t>-9,68; 2,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,34</t>
+          <t>-2,47; 1,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 13,44</t>
+          <t>-7,42; 12,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 9,6</t>
+          <t>-5,74; 9,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 2,98</t>
+          <t>-11,28; 3,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,47</t>
+          <t>-2,55; 2,07</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,3</t>
+          <t>5,65; 10,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,41</t>
+          <t>6,1; 10,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,07</t>
+          <t>2,83; 7,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,8</t>
+          <t>0,32; 2,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 16,75</t>
+          <t>8,72; 16,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,95</t>
+          <t>8,42; 14,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,94</t>
+          <t>3,86; 10,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,0</t>
+          <t>0,33; 2,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P36B08_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
